--- a/www/download/COUNTRY.IRL.rpO2.xlsx
+++ b/www/download/COUNTRY.IRL.rpO2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>Irlanda</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.791728047333354</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.793285656462526</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.83647008002156</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.890583022093105</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>0.938262390790355</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>1.08271976714892</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>1.11656986366326</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1.05752964034084</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>0.884016998033016</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>0.803923180836867</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>0.80379392216222</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>0.796431997410537</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>0.729660720781679</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.679902076537751</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.716948691519964</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>-0.768959355081463</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.331</t>
+          <t>-0.746112048287399</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>-0.795442872333533</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.526</t>
+          <t>-0.807309305690137</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.622</t>
+          <t>-0.834749854758227</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.697</t>
+          <t>-0.869607555432485</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.748</t>
+          <t>-0.868471359104227</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.779</t>
+          <t>-0.873017861155265</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.814</t>
+          <t>-0.896033820993383</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1.871</t>
+          <t>-0.911032641302777</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1.962</t>
+          <t>-0.932239864891234</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2.048</t>
+          <t>-0.940114454564126</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2.123</t>
+          <t>-0.932561011131008</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.177</t>
+          <t>-0.918976171815329</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.002</t>
+          <t>-0.912394990520109</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.018</t>
+          <t>-0.715310780047071</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.063</t>
+          <t>-0.687818871814097</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.122</t>
+          <t>-0.749774686860856</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.224</t>
+          <t>-0.763661859526774</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.311</t>
+          <t>-0.797407235672345</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.381</t>
+          <t>-0.839989075689461</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>-0.838031643759925</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>-0.844168647633015</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.494</t>
+          <t>-0.871127493381395</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.541</t>
+          <t>-0.891251006681596</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-0.908963383964418</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.714</t>
+          <t>-0.912435527797614</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1.762</t>
+          <t>-0.900792626332722</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-0.887551923778398</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>-0.879210034316528</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2547.899</t>
+          <t>-0.704872271186603</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2653.568</t>
+          <t>-0.661558028879326</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2769.255</t>
+          <t>-0.719981437904439</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2978.043</t>
+          <t>-0.724153030051276</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3146.232</t>
+          <t>-0.754872181097043</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3278.661</t>
+          <t>-0.802491454177952</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3360.912</t>
+          <t>-0.798586066708271</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3387.924</t>
+          <t>-0.805377746342549</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>3426.525</t>
+          <t>-0.84025413654954</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>3525.15</t>
+          <t>-0.865452909281855</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>3696.057</t>
+          <t>-0.899043512209486</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>3837.868</t>
+          <t>-0.896200017747951</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>3943.674</t>
+          <t>-0.894443175664205</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>3993.21</t>
+          <t>-0.877112393129044</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>3609.214</t>
+          <t>-0.864815169018912</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1929.917</t>
+          <t>132754187903.251</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2034.51</t>
+          <t>130461252054.355</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2130.014</t>
+          <t>110825113121.045</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2308.418</t>
+          <t>116382819439.682</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2458.008</t>
+          <t>168547796543.842</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2578.571</t>
+          <t>225280342678.173</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2667.309</t>
+          <t>207647311040.395</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2691.109</t>
+          <t>176454525241.584</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2729.001</t>
+          <t>208013062505.808</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2809.265</t>
+          <t>227284011065.581</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2977.279</t>
+          <t>251440295400.243</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3109.725</t>
+          <t>256258411572.954</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>3164.381</t>
+          <t>211107527516.8</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3056.794</t>
+          <t>205370322997.503</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2739.318</t>
+          <t>155876319489.624</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>31527806202.1259</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>24.37</t>
+          <t>29757642116.8932</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>23500175132.4701</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>26.39</t>
+          <t>24777989358.1375</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>31308027096.3323</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>43566492721.8094</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>29.28</t>
+          <t>44952143396.244</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>45326520191.0051</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>51271025781.7133</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>53976129911.9365</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>36.56</t>
+          <t>74069777953.2834</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>40.99</t>
+          <t>83004316294.2896</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>41.01</t>
+          <t>74457687859.824</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>72407100439.6407</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>45.29</t>
+          <t>56789213150.414</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>36754245.3922304</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.78</t>
+          <t>32416104.4506263</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>44.99</t>
+          <t>26582241.8450408</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>44.88</t>
+          <t>25409772.7306378</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>30178287.4659488</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>44.31</t>
+          <t>38753883.1369831</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>43.42</t>
+          <t>35223807.6090662</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>42.98</t>
+          <t>25611110.1675969</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>29505455.1654553</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>31266998.9116349</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>38.68</t>
+          <t>34829368.274968</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>37.82</t>
+          <t>30945487.5116825</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>37.03</t>
+          <t>23753761.8911347</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>27085398.1486651</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>35.84</t>
+          <t>26768346.1703559</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>3097.79147668829</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>3280.75498638117</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>1730.88491107493</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>1968.71763961066</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>1940.28583747079</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>1784.13951551553</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>1679.74439916612</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>1709.08881654332</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>24.74</t>
+          <t>1684.38344538899</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>24.33</t>
+          <t>1651.83565110591</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>24.76</t>
+          <t>1557.91308258202</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>21.19</t>
+          <t>1685.40783100843</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>2205.99126143705</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>21.28</t>
+          <t>6365.3628317079</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>3153.76773499361</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>55655.6165849593</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20.14</t>
+          <t>56794.0179578744</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20.56</t>
+          <t>47524.8249543426</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>49089.3400808768</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22.43</t>
+          <t>66200.9752101437</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>22.89</t>
+          <t>69786.0102275696</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>61183.0564373405</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>54634.9591769462</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>65849.3013766742</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>77717.1442123389</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>83111.2922161581</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>89767.2387958788</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>94245.8941335374</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>102590.563948109</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>36.67</t>
+          <t>89929.9433346103</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>-0.728782330895923</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.49</t>
+          <t>-0.699658083851179</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>45.24</t>
+          <t>-0.757115741174333</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>44.73</t>
+          <t>-0.768451997438769</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>44.27</t>
+          <t>-0.799927093141315</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>43.69</t>
+          <t>-0.84133672331979</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>42.76</t>
+          <t>-0.839910525329552</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>-0.846981083159322</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>-0.874871222709913</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>40.92</t>
+          <t>-0.894382011754432</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>-0.917237053839825</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>41.04</t>
+          <t>-0.923071532156494</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>41.06</t>
+          <t>-0.915262545239419</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>40.52</t>
+          <t>-0.901662294261529</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>40.14</t>
+          <t>-0.894865943674478</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>37.71</t>
+          <t>10514.200186931</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>35.37</t>
+          <t>11044.4194937954</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>11151.7031242688</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>11305.0612827041</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>11683.5268741575</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>33.42</t>
+          <t>10878.212509104</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>33.78</t>
+          <t>10639.0917351734</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>11655.9578944585</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>30.94</t>
+          <t>14520.3084097658</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>16623.8437844044</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>29.37</t>
+          <t>18821.696288396</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>21012.9477639421</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>26.54</t>
+          <t>27072.505507697</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.791728047333354</t>
+          <t>30982.389014236</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.793285656462526</t>
+          <t>27986.7514426312</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.83647008002156</t>
+          <t>20942.9987318539</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.890583022093105</t>
+          <t>20246.0853641425</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.938262390790355</t>
+          <t>23888.2983235281</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.08271976714892</t>
+          <t>31539.3928480737</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656986366326</t>
+          <t>31397.5858162627</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05752964034084</t>
+          <t>31020.7876387796</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884016998033016</t>
+          <t>34313.3658938914</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923180836867</t>
+          <t>35022.1677485753</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.80379392216222</t>
+          <t>45447.8550433547</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796431997410537</t>
+          <t>48428.6401970007</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660720781679</t>
+          <t>42260.4346726951</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902076537751</t>
+          <t>41855.6540285242</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948691519964</t>
+          <t>35829.7895170476</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>82818156739.4043</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>85231637519.2391</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>81506716753.8929</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>93230982438.88</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>143438406973.716</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>204713771660.324</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>235741222069.525</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>265859819589.643</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>308500215363.021</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>322863935011.893</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>343847356071.012</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>331015775293.124</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>290910334041.293</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>264448934436.296</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>226984485775.177</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>101483638283.698</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>106441916087.752</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>101376046586.581</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>127904951682.523</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>195511201829.556</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>292780041073.819</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>325059562710.496</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>366427447001.195</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>407114861173.828</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>415153274514.52</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>428114778588.111</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>396778792914.016</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>317473035191.149</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>303435178145.022</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>256957622804.481</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>-18665481544.2933</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>-21210278568.5124</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>-19869329832.688</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>-34673969243.6426</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>-52072794855.8404</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>-88066269413.4954</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>-89318340640.971</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>-100567627411.552</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>-98614645810.8076</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>-92289339502.627</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>-84267422517.0988</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>-65763017620.8915</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-26562701149.8558</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-38986243708.7255</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-29973137029.304</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>8402.97133171687</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>8405.59455506064</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>5086.72472457322</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>4687.94062575136</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>4779.4012854957</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>5004.14341377976</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>5026.42301924581</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>4746.76732403075</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>4293.58951901</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>3698.97090160335</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>3761.39838004863</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>3725.54109009969</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>3581.04167123998</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.562</t>
+          <t>4115.98898934825</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>3766.93110921688</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>9598.02433139638</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>9612.07272944597</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>4989.74610028937</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>5392.38300486409</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>5420.58475772302</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>6064.89639360369</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>5777.81869685803</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>5554.30203502153</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>5234.26151412813</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>4599.86823836139</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>4306.91821199748</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>4176.3025370345</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>4199.77616689907</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>10708.91005475</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>4893.98127366118</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-76.9</t>
+          <t>47267.1435503917</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-74.61</t>
+          <t>52335.3517922755</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-79.54</t>
+          <t>58755.980409501</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-80.73</t>
+          <t>67689.9588631831</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-83.47</t>
+          <t>79579.0265480544</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-86.96</t>
+          <t>88633.6395201882</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-86.85</t>
+          <t>96846.7936380043</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-87.3</t>
+          <t>104885.773008976</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-89.6</t>
+          <t>125481.444754296</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-91.1</t>
+          <t>149748.221083719</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-93.22</t>
+          <t>159911.93169149</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-94.01</t>
+          <t>170932.367972707</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-93.26</t>
+          <t>202338.860603665</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-91.9</t>
+          <t>213772.943765359</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-91.24</t>
+          <t>195689.115276211</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-71.53</t>
+          <t>74025141969.1081</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-68.78</t>
+          <t>74184363526.3311</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-74.98</t>
+          <t>65014332746.0987</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-76.37</t>
+          <t>68007760268.9896</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-79.74</t>
+          <t>106573899285.64</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-84</t>
+          <t>143744891143.537</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-83.8</t>
+          <t>127482838768.315</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-84.42</t>
+          <t>104101218974.031</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-87.11</t>
+          <t>111949080744.684</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-89.13</t>
+          <t>122001626985.421</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-90.9</t>
+          <t>115431014033.501</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-91.24</t>
+          <t>107248911084.905</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-90.08</t>
+          <t>86350469206.8363</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-88.76</t>
+          <t>81812929758.203</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-87.92</t>
+          <t>61677878145.0747</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-70.49</t>
+          <t>37802.9525057756</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-66.16</t>
+          <t>41997.3925849796</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-72</t>
+          <t>46212.1216525593</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-72.42</t>
+          <t>55125.4373668695</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-75.49</t>
+          <t>63494.400704881</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-80.25</t>
+          <t>72614.740911448</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-79.86</t>
+          <t>77624.1208204714</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-80.54</t>
+          <t>80475.6649472791</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-84.03</t>
+          <t>96366.1927540968</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-86.55</t>
+          <t>117771.706854291</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-89.9</t>
+          <t>131133.924261323</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-89.62</t>
+          <t>143958.75462874</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-89.44</t>
+          <t>171829.484913713</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-87.71</t>
+          <t>181990.362949974</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-86.48</t>
+          <t>154971.787825277</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>12334.863</t>
+          <t>117655658451.849</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>12795.236</t>
+          <t>118366234182.015</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>7013.033</t>
+          <t>103441172257.621</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>8230.038</t>
+          <t>114063164555.486</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8790.291</t>
+          <t>170742165075.968</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>10292.457</t>
+          <t>235876135007.5</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10099.928</t>
+          <t>218428662702.67</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>9882.353</t>
+          <t>193798991564.605</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>9497.515</t>
+          <t>218785554691.011</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>8604.541</t>
+          <t>241789078718.315</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>8451.789</t>
+          <t>267426220756.782</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>8551.401</t>
+          <t>271064630876.897</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>8916.133</t>
+          <t>236502672022.639</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>23311.76</t>
+          <t>218108578812.922</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>9796.151</t>
+          <t>156660462095.103</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>8550.898</t>
+          <t>9464.19104461608</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8937.467</t>
+          <t>10337.9592072959</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5707.823</t>
+          <t>12543.8587569417</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>5737.294</t>
+          <t>12564.5214963136</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>6263.888</t>
+          <t>16084.6258431734</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6912.402</t>
+          <t>16018.8986087402</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>7196.365</t>
+          <t>19222.6728175329</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>6935.815</t>
+          <t>24410.1080616971</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>6415.481</t>
+          <t>29115.2520001989</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>5700.85</t>
+          <t>31976.5142294279</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>6130.233</t>
+          <t>28778.0074301669</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>6385.395</t>
+          <t>26973.6133439669</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>6309.355</t>
+          <t>30509.3756899523</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>7120.348</t>
+          <t>31782.5808153854</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>5970.48</t>
+          <t>40717.3274509348</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>132754.188</t>
+          <t>-43630516482.7405</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>130461.252</t>
+          <t>-44181870655.6842</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>110825.113</t>
+          <t>-38426839511.522</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>116382.819</t>
+          <t>-46055404286.4966</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>168547.797</t>
+          <t>-64168265790.3276</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>225280.343</t>
+          <t>-92131243863.9627</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>207647.311</t>
+          <t>-90945823934.3547</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>176454.525</t>
+          <t>-89697772590.5738</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>208013.063</t>
+          <t>-106836473946.327</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>227284.011</t>
+          <t>-119787451732.894</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>251440.295</t>
+          <t>-151995206723.281</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>256258.412</t>
+          <t>-163815719791.992</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>211107.528</t>
+          <t>-150152202815.803</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>205370.323</t>
+          <t>-136295649054.719</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>155876.319</t>
+          <t>-94982583950.0282</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>35628.71028</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>38229.90603</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>41540.18573</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>46418.20626</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>50019.52065</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>48963.72501</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>52428.545</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>61114.62804</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>74132.09013</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>84365.43219</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>87903.43056</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>95997.10793</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>110084.02041</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>111640.89857</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>99658.50712</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>7389.098</t>
+          <t>0.0729840454392032</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>7536.206</t>
+          <t>0.0835338898215211</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>4036.322</t>
+          <t>0.102213453290353</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4667.508</t>
+          <t>0.125557931722302</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>4939.971</t>
+          <t>0.141174537540964</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>5759.486</t>
+          <t>0.159660952077967</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5700.833</t>
+          <t>0.177083898526582</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>5519.844</t>
+          <t>0.196765951483505</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>5320.842</t>
+          <t>0.190329076055617</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>4830.798</t>
+          <t>0.177203258064592</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>4713.224</t>
+          <t>0.160724496978183</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>4811.331</t>
+          <t>0.150805399370741</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>4941.344</t>
+          <t>0.128489329984444</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>12742.465</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>5466.452</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>30216.7274515467</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>32858.690471087</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>34730.506188777</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>36928.6783913506</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>39231.0631348185</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>38677.4118061508</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>41788.0281601937</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>47294.7074669603</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>61157.1850026985</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>73200.7446860464</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>82179.909290841</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>91298.543601515</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>107930.941673357</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>123709.969852541</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>106941.324329402</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>31527.806</t>
+          <t>37408.3853721165</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>29757.642</t>
+          <t>40364.5939571423</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>23500.175</t>
+          <t>42672.3483138855</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>24777.989</t>
+          <t>45441.7179008546</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>31308.027</t>
+          <t>48009.4451438283</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>43566.493</t>
+          <t>47248.0235749582</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>44952.143</t>
+          <t>50629.6601011787</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>45326.52</t>
+          <t>57285.7035400332</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>51271.026</t>
+          <t>73950.0882721045</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>53976.13</t>
+          <t>88451.5230381879</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>74069.778</t>
+          <t>98405.7780784118</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>83004.316</t>
+          <t>108777.262988193</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>74457.688</t>
+          <t>130100.676925427</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>72407.1</t>
+          <t>148319.207223746</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>56789.213</t>
+          <t>127815.480017101</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-72.88</t>
+          <t>165791.087053843</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-69.97</t>
+          <t>178033.329237241</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-75.71</t>
+          <t>181733.881635705</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-76.85</t>
+          <t>185067.896370213</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-79.99</t>
+          <t>186982.497140142</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-84.13</t>
+          <t>177753.198114959</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-83.99</t>
+          <t>184456.723820911</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-84.7</t>
+          <t>207323.147820766</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-87.49</t>
+          <t>272207.674054964</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-89.44</t>
+          <t>329071.438269788</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-91.72</t>
+          <t>370978.698109013</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-92.31</t>
+          <t>435573.725423319</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-91.53</t>
+          <t>549546.964525575</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-90.17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-89.49</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>36.754</t>
+          <t>37408.3853721165</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>32.416</t>
+          <t>39586.9000935393</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>26.582</t>
+          <t>42636.3199305665</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>25.41</t>
+          <t>44339.1547181014</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>30.178</t>
+          <t>47127.5998055457</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>38.754</t>
+          <t>48888.9411973636</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>35.224</t>
+          <t>50252.7586167629</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>25.611</t>
+          <t>51375.7154083659</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>29.505</t>
+          <t>52545.289767832</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>31.267</t>
+          <t>55553.730422125</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>34.829</t>
+          <t>58875.9240749664</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>30.945</t>
+          <t>61543.1947969549</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>23.754</t>
+          <t>67220.7681768881</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>27.085</t>
+          <t>73453.1812739769</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>26.768</t>
+          <t>71293.6854282151</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>30216.7274515467</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>31981.71564716</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>34132.6468725914</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>35349.3904568689</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>37589.0812415935</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>39094.8874637977</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>40432.839510253</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>41172.2473951654</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>42185.0981845677</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>44788.0933941631</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>48212.8678112792</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>50722.3678438831</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>54977.3136530097</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>59860.5071632062</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>56684.3282598564</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>22614.3044178835</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>25916.2360028577</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>29727.3507461145</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>34541.8035791454</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>38080.6944361717</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>39258.4573550418</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>43303.4074988213</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>52450.0943399668</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>66329.3435078955</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>74936.3747818121</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>78447.0609315882</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>86699.8173818071</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>97683.4267745733</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>86698.7595662541</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>74385.0519628989</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>8550898110.10567</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>8937467253.45856</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>5707822619.32336</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>5737293943.36017</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>6263887989.17367</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>6912402488.7068</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>7196365021.61537</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>6935815023.78472</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>6415480766.4743</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>5700850254.58018</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>6130233044.84375</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>6385394876.91745</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>6309354956.59929</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>7120348136.40928</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>5970480334.0377</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>12334863121.1215</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>12795235570.7475</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>7013033256.7496</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>8230038283.04573</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>8790291272.36153</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>10292456684.3507</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10099927528.6801</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>9882353038.26119</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>9497515174.77036</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>8604541125.88824</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>8451788626.26855</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>8551401251.13438</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>8916133201.87906</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>23311759887.6766</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>9796151407.19007</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>7389097758.95833</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>7536205723.71416</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>4036322411.57493</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>4667508448.90217</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>4939971073.42936</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>5759486179.68449</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5700833335.76541</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>5519844075.33162</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>5320842462.78066</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>4830798097.50484</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>4713223862.21025</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>4811331387.93465</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>4941343760.45909</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>12742464515.5998</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>5466451871.61744</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1285146.05664965</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1331163</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1405489</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1526234</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1621650</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1697054</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1748052</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1779225</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1814490</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1870606</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1962375</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2047601</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2123002</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2176856.4465005</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2001673.25116501</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1017604.10366158</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1063276.0353731</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1122101.73114926</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1223841</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1310600.97593877</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1381335.80857661</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1431707</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1461166</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1494199.83863608</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1541199</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>1629775</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1713951</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1761877</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>1729924</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1584972</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2547899286.28545</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2653568154.19399</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2769255347.01174</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2978042757.53249</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>3146232450.2526</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>3278660739.29116</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3360911560.89258</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>3387924434.28586</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>3426524671.01494</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>3525150168.57143</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>3696056554.17269</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>3837868146.12786</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>3943673918.4152</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>3993210073.6081</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>3609213724.27385</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1929917147.60251</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2034509849.31277</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2130014101.6263</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2308418033.48914</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2458008026.38916</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2578571039.99907</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2667309175.65362</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2691108649.85751</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2729000750.27981</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2809265001.64934</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2977278513.48593</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>3109725073.94992</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>3164381155.58501</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>3056793726.46356</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2739317842.58637</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.228551949077892</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.243723137843603</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.249858280534478</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.263939145793767</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.276483269509155</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.28420368499428</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.292821454861932</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.310523354271164</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.331000979590364</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.348869083619875</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.365645356771562</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.409887125460397</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.41008319108744</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.42418374560626</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.452934382739975</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.420987678638385</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.437758976405333</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.449934012124202</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.448791732503489</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.446990165169487</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.443127372849649</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.434154610173299</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.429782298577874</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.421636914152267</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.407857989703823</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.38679683229293</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.378179481889638</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.370278519530993</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.362968876895351</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.358388550232721</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.350460372283722</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.318517885751064</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.300207707341319</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.287269121702744</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.276526565321358</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.272668942156071</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.273023934964769</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.259694347150962</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.247362106257369</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.243272926676302</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.247557810935509</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.211933392649964</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.219638289381567</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.212847377498389</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.188677067027303</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.189554344070667</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.201418712090427</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.205601942560401</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.2151627525334</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.224272432322089</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.228917850140343</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.234596609399241</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.251870921354052</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.268609409539807</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.287257104030716</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.294773786798651</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.310305463091801</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.323984639496917</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.338950725981488</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.366725580736755</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.433327810946452</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.44490994834356</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.452400829696932</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.447331669379548</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.4427128045549</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.436900933409306</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.427572595839524</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.424523639477111</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.422019268911282</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.409196985907454</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.411506251883783</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.410382874176191</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.410621569332512</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.405243912708142</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.401421265114714</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.377117844982881</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.353671339566012</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.341997227742667</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.337505578087051</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.333014763123011</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.334181216450352</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.337830794761235</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.323605439168837</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.309371321548911</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.303545910061829</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.293719961317566</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.279311662732008</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.265393791170571</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.25580536131037</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.231853154148531</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>134723.39307</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>149876.90979</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>164938.59555</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>178120.27518</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>195301.38045</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>206241.77683</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>224824.28026</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>249407.63682</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>318780.68156</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>379865.20657</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>417431.60801</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>463706.59768</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>550941.06294</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>561762.81601</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>482054.72113</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>60022.68979</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>66280.82996</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>72399.69906</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>79983.52148</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>86090.13958</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>86506.48093</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>93933.0676</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>109735.79788</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>140279.43178</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>163387.89782</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>176852.83901</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>195477.08037</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>227784.1037</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>235017.96679</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>202200.53198</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>131261.45336144</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>136759.567012045</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>144311.489342752</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>154908.383914814</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>169219.619632582</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>186069.652263705</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>203826.797026311</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>223182.255285232</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>244092.347013215</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>268622.229508064</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>299043.02653643</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>329852.481077754</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>361935.230409352</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO2</t>
